--- a/public/templates/sufaraa-bible-bank.xlsx
+++ b/public/templates/sufaraa-bible-bank.xlsx
@@ -6248,7 +6248,7 @@
         <v/>
       </c>
       <c r="S95" t="str">
-        <v/>
+        <v>موسى</v>
       </c>
       <c r="T95" t="str">
         <v/>
@@ -6372,7 +6372,7 @@
         <v/>
       </c>
       <c r="S97" t="str">
-        <v/>
+        <v>الناصرة</v>
       </c>
       <c r="T97" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
         <v/>
       </c>
       <c r="S99" t="str">
-        <v/>
+        <v>بطرس</v>
       </c>
       <c r="T99" t="str">
         <v/>
@@ -6620,7 +6620,7 @@
         <v/>
       </c>
       <c r="S101" t="str">
-        <v/>
+        <v>إبراهيم</v>
       </c>
       <c r="T101" t="str">
         <v/>
@@ -6744,7 +6744,7 @@
         <v/>
       </c>
       <c r="S103" t="str">
-        <v/>
+        <v>الفلك</v>
       </c>
       <c r="T103" t="str">
         <v/>
